--- a/administrative_forms/032_harassment_reporting_monitoring_form--administrative_forms.xlsx
+++ b/administrative_forms/032_harassment_reporting_monitoring_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -857,8 +857,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -886,12 +886,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'jane_smith'}</t>
+          <t>jane_smith</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Jane Smith'}</t>
+          <t>Jane Smith</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'witness_1'}</t>
+          <t>witness_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Witness 1'}</t>
+          <t>Witness 1</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'witness_2'}</t>
+          <t>witness_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Witness 2'}</t>
+          <t>Witness 2</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'witness_3'}</t>
+          <t>witness_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Witness 3'}</t>
+          <t>Witness 3</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'bullying'}</t>
+          <t>bullying</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Bullying'}</t>
+          <t>Bullying</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'harassment'}</t>
+          <t>harassment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Harassment'}</t>
+          <t>Harassment</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'perpetrator_1'}</t>
+          <t>perpetrator_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Perpetrator 1'}</t>
+          <t>Perpetrator 1</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'perpetrator_2'}</t>
+          <t>perpetrator_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Perpetrator 2'}</t>
+          <t>Perpetrator 2</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'perpetrator_3'}</t>
+          <t>perpetrator_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Perpetrator 3'}</t>
+          <t>Perpetrator 3</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'follow_up_1'}</t>
+          <t>follow_up_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Follow Up 1'}</t>
+          <t>Follow Up 1</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'follow_up_2'}</t>
+          <t>follow_up_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Follow Up 2'}</t>
+          <t>Follow Up 2</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'follow_up_3'}</t>
+          <t>follow_up_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Follow Up 3'}</t>
+          <t>Follow Up 3</t>
         </is>
       </c>
     </row>
